--- a/design/Общий список элементов игры.xlsx
+++ b/design/Общий список элементов игры.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Атрибуты" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
   <si>
     <t>Сила</t>
   </si>
@@ -235,6 +235,18 @@
   </si>
   <si>
     <t>Механика покупок</t>
+  </si>
+  <si>
+    <t>состояние</t>
+  </si>
+  <si>
+    <t>Плохой статус</t>
+  </si>
+  <si>
+    <t>Оглушение</t>
+  </si>
+  <si>
+    <t>Смерть?</t>
   </si>
 </sst>
 </file>
@@ -283,14 +295,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -594,174 +606,201 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="3"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="3"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="3"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1"/>
+      <c r="B12" s="3"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="1"/>
+      <c r="B13" s="3"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>30</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -777,42 +816,42 @@
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -826,170 +865,170 @@
   <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>72</v>
       </c>
     </row>
